--- a/BD_Treinamentos.xlsx
+++ b/BD_Treinamentos.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_Treinamentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_156950B7D30053BD442A4FF1525ED87656CC5D60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90438A43-7436-490B-B4B1-218C01909D71}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_156950B7D30053BD442A4FF1525ED87656CC5D60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E93C8BC2-F6C3-46EE-8CDD-A5B29FB4ACEC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$229</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="143">
   <si>
     <t>ID</t>
   </si>
@@ -385,15 +388,9 @@
     <t>SALA DE CGRSS</t>
   </si>
   <si>
-    <t>HOSPITAL DA CIDADE</t>
-  </si>
-  <si>
     <t>PAPEL DO AUXILIAR DE TRANSPORTE NA SEGREGAÇÃO CORRETA</t>
   </si>
   <si>
-    <t>ANEXO</t>
-  </si>
-  <si>
     <t>TREINAMENTO INTERNO, LUVAS AS VEZES</t>
   </si>
   <si>
@@ -413,6 +410,48 @@
   </si>
   <si>
     <t xml:space="preserve">TREINAMENTO INTERNO, EDUCAÇÃO AMBIENTAL </t>
+  </si>
+  <si>
+    <t>ACOMPANHANTE</t>
+  </si>
+  <si>
+    <t>COLABORADORES</t>
+  </si>
+  <si>
+    <t>CENTRO CIRÚRGICO</t>
+  </si>
+  <si>
+    <t>II SEMANA DO MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t>AUDITÓRIO ANEXO</t>
+  </si>
+  <si>
+    <t>CORREDOR H. CID.</t>
+  </si>
+  <si>
+    <t>COLABORADORES EXTERNOS</t>
+  </si>
+  <si>
+    <t>SETOR MAXTEC</t>
+  </si>
+  <si>
+    <t>INTRODUÇÃO TEÓRICA SOBRE SANEANTES</t>
+  </si>
+  <si>
+    <t>ANTIGO C.C ANEXO</t>
+  </si>
+  <si>
+    <t>INTRODUÇÃO A BOAS PRÁTICAS DE MANEJO DE RSS</t>
+  </si>
+  <si>
+    <t>RN EMPREDIMENTOS</t>
+  </si>
+  <si>
+    <t>SALA DA RN</t>
+  </si>
+  <si>
+    <t>TREINAMENTO SOBRE BOAS PRÁTICAS DE MANEJO DE RSS</t>
   </si>
 </sst>
 </file>
@@ -420,7 +459,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -453,7 +492,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,6 +508,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -756,8 +799,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -766,7 +812,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -5771,7 +5817,7 @@
         <v>108</v>
       </c>
       <c r="E196" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -5794,10 +5840,10 @@
         <v>46147</v>
       </c>
       <c r="D197" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E197" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -5820,10 +5866,10 @@
         <v>46148</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E198" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F198" t="s">
         <v>10</v>
@@ -5849,7 +5895,7 @@
         <v>108</v>
       </c>
       <c r="E199" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F199" t="s">
         <v>13</v>
@@ -5872,10 +5918,10 @@
         <v>46154</v>
       </c>
       <c r="D200" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E200" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F200" t="s">
         <v>10</v>
@@ -5898,10 +5944,10 @@
         <v>46155</v>
       </c>
       <c r="D201" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E201" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F201" t="s">
         <v>10</v>
@@ -5921,10 +5967,10 @@
         <v>46160</v>
       </c>
       <c r="D202" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E202" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F202" t="s">
         <v>10</v>
@@ -5944,10 +5990,10 @@
         <v>46162</v>
       </c>
       <c r="D203" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E203" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F203" t="s">
         <v>10</v>
@@ -5967,10 +6013,10 @@
         <v>46162</v>
       </c>
       <c r="D204" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E204" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -5990,10 +6036,10 @@
         <v>46162</v>
       </c>
       <c r="D205" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E205" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F205" t="s">
         <v>13</v>
@@ -6016,7 +6062,7 @@
         <v>108</v>
       </c>
       <c r="E206" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F206" t="s">
         <v>13</v>
@@ -6042,7 +6088,7 @@
         <v>108</v>
       </c>
       <c r="E207" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F207" t="s">
         <v>13</v>
@@ -6068,7 +6114,7 @@
         <v>108</v>
       </c>
       <c r="E208" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F208" t="s">
         <v>13</v>
@@ -6091,10 +6137,10 @@
         <v>46169</v>
       </c>
       <c r="D209" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E209" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F209" t="s">
         <v>10</v>
@@ -6114,10 +6160,10 @@
         <v>46167</v>
       </c>
       <c r="D210" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E210" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F210" t="s">
         <v>10</v>
@@ -6126,7 +6172,7 @@
         <v>4</v>
       </c>
       <c r="H210" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -6140,10 +6186,10 @@
         <v>46168</v>
       </c>
       <c r="D211" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E211" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F211" t="s">
         <v>10</v>
@@ -6152,7 +6198,7 @@
         <v>7</v>
       </c>
       <c r="H211" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -6169,7 +6215,7 @@
         <v>108</v>
       </c>
       <c r="E212" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F212" t="s">
         <v>13</v>
@@ -6178,7 +6224,7 @@
         <v>16</v>
       </c>
       <c r="H212" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -6192,16 +6238,432 @@
         <v>46167</v>
       </c>
       <c r="D213" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E213" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="F213" t="s">
         <v>10</v>
       </c>
       <c r="G213">
         <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>2026</v>
+      </c>
+      <c r="C214" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D214" t="s">
+        <v>108</v>
+      </c>
+      <c r="E214" t="s">
+        <v>12</v>
+      </c>
+      <c r="F214" t="s">
+        <v>129</v>
+      </c>
+      <c r="G214">
+        <v>20</v>
+      </c>
+      <c r="H214" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>2026</v>
+      </c>
+      <c r="C215" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D215" t="s">
+        <v>108</v>
+      </c>
+      <c r="E215" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" t="s">
+        <v>130</v>
+      </c>
+      <c r="G215">
+        <v>25</v>
+      </c>
+      <c r="H215" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>2026</v>
+      </c>
+      <c r="C216" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D216" t="s">
+        <v>132</v>
+      </c>
+      <c r="E216" t="s">
+        <v>12</v>
+      </c>
+      <c r="F216" t="s">
+        <v>130</v>
+      </c>
+      <c r="G216">
+        <v>40</v>
+      </c>
+      <c r="H216" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>2026</v>
+      </c>
+      <c r="C217" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D217" t="s">
+        <v>132</v>
+      </c>
+      <c r="E217" t="s">
+        <v>9</v>
+      </c>
+      <c r="F217" t="s">
+        <v>130</v>
+      </c>
+      <c r="G217">
+        <v>33</v>
+      </c>
+      <c r="H217" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>2026</v>
+      </c>
+      <c r="C218" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D218" t="s">
+        <v>132</v>
+      </c>
+      <c r="E218" t="s">
+        <v>9</v>
+      </c>
+      <c r="F218" t="s">
+        <v>77</v>
+      </c>
+      <c r="G218">
+        <v>3</v>
+      </c>
+      <c r="H218" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>2026</v>
+      </c>
+      <c r="C219" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D219" t="s">
+        <v>132</v>
+      </c>
+      <c r="E219" t="s">
+        <v>9</v>
+      </c>
+      <c r="F219" t="s">
+        <v>135</v>
+      </c>
+      <c r="G219">
+        <v>4</v>
+      </c>
+      <c r="H219" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>2026</v>
+      </c>
+      <c r="C220" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D220" t="s">
+        <v>132</v>
+      </c>
+      <c r="E220" t="s">
+        <v>9</v>
+      </c>
+      <c r="F220" t="s">
+        <v>77</v>
+      </c>
+      <c r="G220">
+        <v>14</v>
+      </c>
+      <c r="H220" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>2026</v>
+      </c>
+      <c r="C221" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D221" t="s">
+        <v>132</v>
+      </c>
+      <c r="E221" t="s">
+        <v>12</v>
+      </c>
+      <c r="F221" t="s">
+        <v>77</v>
+      </c>
+      <c r="G221">
+        <v>9</v>
+      </c>
+      <c r="H221" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>2026</v>
+      </c>
+      <c r="C222" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D222" t="s">
+        <v>132</v>
+      </c>
+      <c r="E222" t="s">
+        <v>12</v>
+      </c>
+      <c r="F222" t="s">
+        <v>130</v>
+      </c>
+      <c r="G222">
+        <v>30</v>
+      </c>
+      <c r="H222" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>2026</v>
+      </c>
+      <c r="C223" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D223" t="s">
+        <v>132</v>
+      </c>
+      <c r="E223" t="s">
+        <v>9</v>
+      </c>
+      <c r="F223" t="s">
+        <v>130</v>
+      </c>
+      <c r="G223">
+        <v>13</v>
+      </c>
+      <c r="H223" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>2026</v>
+      </c>
+      <c r="C224" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D224" t="s">
+        <v>132</v>
+      </c>
+      <c r="E224" t="s">
+        <v>9</v>
+      </c>
+      <c r="F224" t="s">
+        <v>130</v>
+      </c>
+      <c r="G224">
+        <v>20</v>
+      </c>
+      <c r="H224" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>2026</v>
+      </c>
+      <c r="C225" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D225" t="s">
+        <v>132</v>
+      </c>
+      <c r="E225" t="s">
+        <v>9</v>
+      </c>
+      <c r="F225" t="s">
+        <v>130</v>
+      </c>
+      <c r="G225">
+        <v>13</v>
+      </c>
+      <c r="H225" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>2026</v>
+      </c>
+      <c r="C226" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D226" t="s">
+        <v>137</v>
+      </c>
+      <c r="E226" t="s">
+        <v>12</v>
+      </c>
+      <c r="F226" t="s">
+        <v>130</v>
+      </c>
+      <c r="G226">
+        <v>26</v>
+      </c>
+      <c r="H226" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>2026</v>
+      </c>
+      <c r="C227" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D227" t="s">
+        <v>139</v>
+      </c>
+      <c r="E227" t="s">
+        <v>12</v>
+      </c>
+      <c r="F227" t="s">
+        <v>140</v>
+      </c>
+      <c r="G227">
+        <v>8</v>
+      </c>
+      <c r="H227" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>2026</v>
+      </c>
+      <c r="C228" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D228" t="s">
+        <v>139</v>
+      </c>
+      <c r="E228" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" t="s">
+        <v>140</v>
+      </c>
+      <c r="G228">
+        <v>5</v>
+      </c>
+      <c r="H228" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>2026</v>
+      </c>
+      <c r="C229" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D229" t="s">
+        <v>142</v>
+      </c>
+      <c r="E229" t="s">
+        <v>12</v>
+      </c>
+      <c r="F229" t="s">
+        <v>140</v>
+      </c>
+      <c r="G229">
+        <v>13</v>
+      </c>
+      <c r="H229" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/BD_Treinamentos.xlsx
+++ b/BD_Treinamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_Treinamentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_156950B7D30053BD442A4FF1525ED87656CC5D60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E93C8BC2-F6C3-46EE-8CDD-A5B29FB4ACEC}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_156950B7D30053BD442A4FF1525ED87656CC5D60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D3389F7-6B73-4C13-B200-5F95BEBF0671}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="138">
   <si>
     <t>ID</t>
   </si>
@@ -136,9 +136,6 @@
     <t>Posto de Enfermagem</t>
   </si>
   <si>
-    <t>Colaborador interno</t>
-  </si>
-  <si>
     <t>Descarte correto de material perfurocortante.</t>
   </si>
   <si>
@@ -412,12 +409,6 @@
     <t xml:space="preserve">TREINAMENTO INTERNO, EDUCAÇÃO AMBIENTAL </t>
   </si>
   <si>
-    <t>ACOMPANHANTE</t>
-  </si>
-  <si>
-    <t>COLABORADORES</t>
-  </si>
-  <si>
     <t>CENTRO CIRÚRGICO</t>
   </si>
   <si>
@@ -430,9 +421,6 @@
     <t>CORREDOR H. CID.</t>
   </si>
   <si>
-    <t>COLABORADORES EXTERNOS</t>
-  </si>
-  <si>
     <t>SETOR MAXTEC</t>
   </si>
   <si>
@@ -443,9 +431,6 @@
   </si>
   <si>
     <t>INTRODUÇÃO A BOAS PRÁTICAS DE MANEJO DE RSS</t>
-  </si>
-  <si>
-    <t>RN EMPREDIMENTOS</t>
   </si>
   <si>
     <t>SALA DA RN</t>
@@ -803,6 +788,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1758,7 +1746,7 @@
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>10</v>
@@ -1836,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -1882,7 +1870,7 @@
         <v>45848</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -1894,7 +1882,7 @@
         <v>3</v>
       </c>
       <c r="H42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1934,7 +1922,7 @@
         <v>45848</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -1946,7 +1934,7 @@
         <v>4</v>
       </c>
       <c r="H44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2070,7 +2058,7 @@
         <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G49">
         <v>13</v>
@@ -2284,7 +2272,7 @@
         <v>3</v>
       </c>
       <c r="H57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -2310,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -2336,7 +2324,7 @@
         <v>11</v>
       </c>
       <c r="H59" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -2362,7 +2350,7 @@
         <v>17</v>
       </c>
       <c r="H60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -2388,7 +2376,7 @@
         <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -2414,7 +2402,7 @@
         <v>11</v>
       </c>
       <c r="H62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -2440,7 +2428,7 @@
         <v>4</v>
       </c>
       <c r="H63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -2492,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="H65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -2518,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="H66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -2544,7 +2532,7 @@
         <v>13</v>
       </c>
       <c r="H67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -2570,7 +2558,7 @@
         <v>7</v>
       </c>
       <c r="H68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -2596,7 +2584,7 @@
         <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -2622,7 +2610,7 @@
         <v>10</v>
       </c>
       <c r="H70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -2648,7 +2636,7 @@
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -2674,7 +2662,7 @@
         <v>9</v>
       </c>
       <c r="H72" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -2700,7 +2688,7 @@
         <v>19</v>
       </c>
       <c r="H73" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -2726,7 +2714,7 @@
         <v>7</v>
       </c>
       <c r="H74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -2752,7 +2740,7 @@
         <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -2778,7 +2766,7 @@
         <v>18</v>
       </c>
       <c r="H76" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -2804,7 +2792,7 @@
         <v>30</v>
       </c>
       <c r="H77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -2818,7 +2806,7 @@
         <v>45910</v>
       </c>
       <c r="D78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -2830,7 +2818,7 @@
         <v>4</v>
       </c>
       <c r="H78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -2856,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="H79" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -2882,7 +2870,7 @@
         <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -2908,7 +2896,7 @@
         <v>14</v>
       </c>
       <c r="H81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -2934,7 +2922,7 @@
         <v>19</v>
       </c>
       <c r="H82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -2960,7 +2948,7 @@
         <v>16</v>
       </c>
       <c r="H83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -2986,7 +2974,7 @@
         <v>17</v>
       </c>
       <c r="H84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -3038,7 +3026,7 @@
         <v>11</v>
       </c>
       <c r="H86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -3064,7 +3052,7 @@
         <v>6</v>
       </c>
       <c r="H87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -3130,7 +3118,7 @@
         <v>45945</v>
       </c>
       <c r="D90" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -3142,7 +3130,7 @@
         <v>6</v>
       </c>
       <c r="H90" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -3156,7 +3144,7 @@
         <v>45945</v>
       </c>
       <c r="D91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
@@ -3168,7 +3156,7 @@
         <v>10</v>
       </c>
       <c r="H91" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -3194,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="H92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -3220,7 +3208,7 @@
         <v>7</v>
       </c>
       <c r="H93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -3246,7 +3234,7 @@
         <v>7</v>
       </c>
       <c r="H94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -3272,7 +3260,7 @@
         <v>4</v>
       </c>
       <c r="H95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -3298,7 +3286,7 @@
         <v>7</v>
       </c>
       <c r="H96" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -3324,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -3350,7 +3338,7 @@
         <v>8</v>
       </c>
       <c r="H98" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -3376,7 +3364,7 @@
         <v>6</v>
       </c>
       <c r="H99" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -3390,7 +3378,7 @@
         <v>45961</v>
       </c>
       <c r="D100" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -3402,7 +3390,7 @@
         <v>6</v>
       </c>
       <c r="H100" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -3416,7 +3404,7 @@
         <v>45961</v>
       </c>
       <c r="D101" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E101" t="s">
         <v>9</v>
@@ -3442,7 +3430,7 @@
         <v>45961</v>
       </c>
       <c r="D102" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
@@ -3468,7 +3456,7 @@
         <v>45961</v>
       </c>
       <c r="D103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
@@ -3480,7 +3468,7 @@
         <v>3</v>
       </c>
       <c r="H103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -3494,7 +3482,7 @@
         <v>45961</v>
       </c>
       <c r="D104" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
@@ -3506,7 +3494,7 @@
         <v>4</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -3520,7 +3508,7 @@
         <v>45961</v>
       </c>
       <c r="D105" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -3532,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="H105" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -3546,7 +3534,7 @@
         <v>45961</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
@@ -3558,7 +3546,7 @@
         <v>6</v>
       </c>
       <c r="H106" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -3572,7 +3560,7 @@
         <v>45961</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
@@ -3584,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -3598,7 +3586,7 @@
         <v>45961</v>
       </c>
       <c r="D108" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E108" t="s">
         <v>9</v>
@@ -3610,7 +3598,7 @@
         <v>4</v>
       </c>
       <c r="H108" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -3624,7 +3612,7 @@
         <v>45961</v>
       </c>
       <c r="D109" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -3636,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -3650,7 +3638,7 @@
         <v>45961</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
@@ -3662,7 +3650,7 @@
         <v>6</v>
       </c>
       <c r="H110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -3676,7 +3664,7 @@
         <v>45961</v>
       </c>
       <c r="D111" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
@@ -3688,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -3702,7 +3690,7 @@
         <v>45961</v>
       </c>
       <c r="D112" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
@@ -3714,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -3728,7 +3716,7 @@
         <v>45961</v>
       </c>
       <c r="D113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
@@ -3740,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -3754,7 +3742,7 @@
         <v>45961</v>
       </c>
       <c r="D114" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
@@ -3766,7 +3754,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -3780,7 +3768,7 @@
         <v>45961</v>
       </c>
       <c r="D115" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
@@ -3792,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -3806,7 +3794,7 @@
         <v>45961</v>
       </c>
       <c r="D116" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E116" t="s">
         <v>9</v>
@@ -3818,7 +3806,7 @@
         <v>3</v>
       </c>
       <c r="H116" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -3832,7 +3820,7 @@
         <v>45961</v>
       </c>
       <c r="D117" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
@@ -3844,7 +3832,7 @@
         <v>6</v>
       </c>
       <c r="H117" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -3870,7 +3858,7 @@
         <v>17</v>
       </c>
       <c r="H118" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -3896,7 +3884,7 @@
         <v>5</v>
       </c>
       <c r="H119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -3922,7 +3910,7 @@
         <v>6</v>
       </c>
       <c r="H120" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -3948,7 +3936,7 @@
         <v>30</v>
       </c>
       <c r="H121" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -3974,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="H122" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -3988,7 +3976,7 @@
         <v>45986</v>
       </c>
       <c r="D123" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E123" t="s">
         <v>12</v>
@@ -4000,7 +3988,7 @@
         <v>14</v>
       </c>
       <c r="H123" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -4014,7 +4002,7 @@
         <v>45986</v>
       </c>
       <c r="D124" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
@@ -4026,7 +4014,7 @@
         <v>19</v>
       </c>
       <c r="H124" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -4040,7 +4028,7 @@
         <v>45986</v>
       </c>
       <c r="D125" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E125" t="s">
         <v>9</v>
@@ -4052,7 +4040,7 @@
         <v>10</v>
       </c>
       <c r="H125" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -4066,7 +4054,7 @@
         <v>45987</v>
       </c>
       <c r="D126" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E126" t="s">
         <v>12</v>
@@ -4078,7 +4066,7 @@
         <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -4092,7 +4080,7 @@
         <v>45987</v>
       </c>
       <c r="D127" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E127" t="s">
         <v>9</v>
@@ -4104,7 +4092,7 @@
         <v>16</v>
       </c>
       <c r="H127" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -4124,13 +4112,13 @@
         <v>9</v>
       </c>
       <c r="F128" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G128">
         <v>5</v>
       </c>
       <c r="H128" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -4144,7 +4132,7 @@
         <v>45988</v>
       </c>
       <c r="D129" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E129" t="s">
         <v>12</v>
@@ -4156,7 +4144,7 @@
         <v>17</v>
       </c>
       <c r="H129" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -4170,7 +4158,7 @@
         <v>45988</v>
       </c>
       <c r="D130" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E130" t="s">
         <v>12</v>
@@ -4182,7 +4170,7 @@
         <v>20</v>
       </c>
       <c r="H130" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -4196,7 +4184,7 @@
         <v>45961</v>
       </c>
       <c r="D131" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E131" t="s">
         <v>12</v>
@@ -4208,7 +4196,7 @@
         <v>31</v>
       </c>
       <c r="H131" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -4222,13 +4210,13 @@
         <v>45992</v>
       </c>
       <c r="D132" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E132" t="s">
         <v>12</v>
       </c>
       <c r="F132" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G132">
         <v>5</v>
@@ -4245,7 +4233,7 @@
         <v>45992</v>
       </c>
       <c r="D133" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E133" t="s">
         <v>12</v>
@@ -4268,7 +4256,7 @@
         <v>45992</v>
       </c>
       <c r="D134" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E134" t="s">
         <v>12</v>
@@ -4291,7 +4279,7 @@
         <v>46027</v>
       </c>
       <c r="D135" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E135" t="s">
         <v>12</v>
@@ -4303,7 +4291,7 @@
         <v>29</v>
       </c>
       <c r="H135" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -4317,7 +4305,7 @@
         <v>46028</v>
       </c>
       <c r="D136" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E136" t="s">
         <v>12</v>
@@ -4329,7 +4317,7 @@
         <v>22</v>
       </c>
       <c r="H136" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -4343,7 +4331,7 @@
         <v>46029</v>
       </c>
       <c r="D137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
@@ -4369,7 +4357,7 @@
         <v>46030</v>
       </c>
       <c r="D138" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E138" t="s">
         <v>12</v>
@@ -4381,7 +4369,7 @@
         <v>20</v>
       </c>
       <c r="H138" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -4395,7 +4383,7 @@
         <v>46034</v>
       </c>
       <c r="D139" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
@@ -4407,7 +4395,7 @@
         <v>26</v>
       </c>
       <c r="H139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -4421,7 +4409,7 @@
         <v>46048</v>
       </c>
       <c r="D140" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E140" t="s">
         <v>9</v>
@@ -4433,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="H140" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -4447,7 +4435,7 @@
         <v>46048</v>
       </c>
       <c r="D141" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
@@ -4459,7 +4447,7 @@
         <v>6</v>
       </c>
       <c r="H141" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -4473,7 +4461,7 @@
         <v>46048</v>
       </c>
       <c r="D142" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E142" t="s">
         <v>9</v>
@@ -4485,7 +4473,7 @@
         <v>56</v>
       </c>
       <c r="H142" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -4499,7 +4487,7 @@
         <v>46049</v>
       </c>
       <c r="D143" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
@@ -4511,7 +4499,7 @@
         <v>15</v>
       </c>
       <c r="H143" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -4525,7 +4513,7 @@
         <v>46049</v>
       </c>
       <c r="D144" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -4537,7 +4525,7 @@
         <v>20</v>
       </c>
       <c r="H144" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -4551,7 +4539,7 @@
         <v>46050</v>
       </c>
       <c r="D145" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E145" t="s">
         <v>12</v>
@@ -4563,7 +4551,7 @@
         <v>26</v>
       </c>
       <c r="H145" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -4577,7 +4565,7 @@
         <v>46051</v>
       </c>
       <c r="D146" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E146" t="s">
         <v>12</v>
@@ -4589,7 +4577,7 @@
         <v>29</v>
       </c>
       <c r="H146" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -4603,7 +4591,7 @@
         <v>46051</v>
       </c>
       <c r="D147" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E147" t="s">
         <v>12</v>
@@ -4615,7 +4603,7 @@
         <v>8</v>
       </c>
       <c r="H147" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -4629,7 +4617,7 @@
         <v>46041</v>
       </c>
       <c r="D148" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E148" t="s">
         <v>9</v>
@@ -4641,7 +4629,7 @@
         <v>4</v>
       </c>
       <c r="H148" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -4655,7 +4643,7 @@
         <v>46042</v>
       </c>
       <c r="D149" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E149" t="s">
         <v>9</v>
@@ -4667,7 +4655,7 @@
         <v>4</v>
       </c>
       <c r="H149" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -4681,7 +4669,7 @@
         <v>46043</v>
       </c>
       <c r="D150" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E150" t="s">
         <v>9</v>
@@ -4693,7 +4681,7 @@
         <v>4</v>
       </c>
       <c r="H150" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -4707,7 +4695,7 @@
         <v>46044</v>
       </c>
       <c r="D151" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E151" t="s">
         <v>9</v>
@@ -4719,7 +4707,7 @@
         <v>4</v>
       </c>
       <c r="H151" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -4733,7 +4721,7 @@
         <v>46045</v>
       </c>
       <c r="D152" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
@@ -4745,7 +4733,7 @@
         <v>4</v>
       </c>
       <c r="H152" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -4759,7 +4747,7 @@
         <v>46058</v>
       </c>
       <c r="D153" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E153" t="s">
         <v>9</v>
@@ -4785,7 +4773,7 @@
         <v>46059</v>
       </c>
       <c r="D154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E154" t="s">
         <v>9</v>
@@ -4797,7 +4785,7 @@
         <v>19</v>
       </c>
       <c r="H154" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -4811,7 +4799,7 @@
         <v>46064</v>
       </c>
       <c r="D155" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E155" t="s">
         <v>9</v>
@@ -4834,7 +4822,7 @@
         <v>46064</v>
       </c>
       <c r="D156" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
@@ -4846,7 +4834,7 @@
         <v>8</v>
       </c>
       <c r="H156" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -4860,7 +4848,7 @@
         <v>46065</v>
       </c>
       <c r="D157" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
@@ -4883,7 +4871,7 @@
         <v>46073</v>
       </c>
       <c r="D158" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E158" t="s">
         <v>12</v>
@@ -4895,7 +4883,7 @@
         <v>20</v>
       </c>
       <c r="H158" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -4909,7 +4897,7 @@
         <v>46073</v>
       </c>
       <c r="D159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E159" t="s">
         <v>12</v>
@@ -4921,7 +4909,7 @@
         <v>27</v>
       </c>
       <c r="H159" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -4935,7 +4923,7 @@
         <v>46077</v>
       </c>
       <c r="D160" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E160" t="s">
         <v>9</v>
@@ -4947,7 +4935,7 @@
         <v>17</v>
       </c>
       <c r="H160" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -4961,7 +4949,7 @@
         <v>46062</v>
       </c>
       <c r="D161" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E161" t="s">
         <v>9</v>
@@ -4973,7 +4961,7 @@
         <v>5</v>
       </c>
       <c r="H161" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -4987,7 +4975,7 @@
         <v>46063</v>
       </c>
       <c r="D162" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E162" t="s">
         <v>9</v>
@@ -4999,7 +4987,7 @@
         <v>5</v>
       </c>
       <c r="H162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -5013,7 +5001,7 @@
         <v>46079</v>
       </c>
       <c r="D163" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E163" t="s">
         <v>9</v>
@@ -5025,7 +5013,7 @@
         <v>17</v>
       </c>
       <c r="H163" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -5039,7 +5027,7 @@
         <v>46080</v>
       </c>
       <c r="D164" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E164" t="s">
         <v>9</v>
@@ -5051,7 +5039,7 @@
         <v>5</v>
       </c>
       <c r="H164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -5065,7 +5053,7 @@
         <v>46080</v>
       </c>
       <c r="D165" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E165" t="s">
         <v>9</v>
@@ -5077,7 +5065,7 @@
         <v>5</v>
       </c>
       <c r="H165" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -5091,7 +5079,7 @@
         <v>46083</v>
       </c>
       <c r="D166" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E166" t="s">
         <v>9</v>
@@ -5117,7 +5105,7 @@
         <v>46084</v>
       </c>
       <c r="D167" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E167" t="s">
         <v>9</v>
@@ -5129,7 +5117,7 @@
         <v>9</v>
       </c>
       <c r="H167" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -5143,7 +5131,7 @@
         <v>46088</v>
       </c>
       <c r="D168" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E168" t="s">
         <v>9</v>
@@ -5155,7 +5143,7 @@
         <v>25</v>
       </c>
       <c r="H168" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -5169,7 +5157,7 @@
         <v>46091</v>
       </c>
       <c r="D169" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E169" t="s">
         <v>12</v>
@@ -5181,7 +5169,7 @@
         <v>19</v>
       </c>
       <c r="H169" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -5195,7 +5183,7 @@
         <v>46093</v>
       </c>
       <c r="D170" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E170" t="s">
         <v>12</v>
@@ -5207,7 +5195,7 @@
         <v>27</v>
       </c>
       <c r="H170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -5221,7 +5209,7 @@
         <v>46097</v>
       </c>
       <c r="D171" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E171" t="s">
         <v>12</v>
@@ -5233,7 +5221,7 @@
         <v>29</v>
       </c>
       <c r="H171" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -5247,7 +5235,7 @@
         <v>46100</v>
       </c>
       <c r="D172" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E172" t="s">
         <v>9</v>
@@ -5273,19 +5261,19 @@
         <v>46097</v>
       </c>
       <c r="D173" t="s">
+        <v>113</v>
+      </c>
+      <c r="E173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173">
+        <v>12</v>
+      </c>
+      <c r="H173" t="s">
         <v>114</v>
-      </c>
-      <c r="E173" t="s">
-        <v>9</v>
-      </c>
-      <c r="F173" t="s">
-        <v>10</v>
-      </c>
-      <c r="G173">
-        <v>12</v>
-      </c>
-      <c r="H173" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -5299,7 +5287,7 @@
         <v>46107</v>
       </c>
       <c r="D174" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E174" t="s">
         <v>12</v>
@@ -5322,7 +5310,7 @@
         <v>46106</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E175" t="s">
         <v>9</v>
@@ -5345,7 +5333,7 @@
         <v>46106</v>
       </c>
       <c r="D176" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E176" t="s">
         <v>9</v>
@@ -5368,7 +5356,7 @@
         <v>46105</v>
       </c>
       <c r="D177" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E177" t="s">
         <v>9</v>
@@ -5380,7 +5368,7 @@
         <v>2</v>
       </c>
       <c r="H177" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -5394,7 +5382,7 @@
         <v>46105</v>
       </c>
       <c r="D178" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E178" t="s">
         <v>9</v>
@@ -5417,7 +5405,7 @@
         <v>46105</v>
       </c>
       <c r="D179" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E179" t="s">
         <v>9</v>
@@ -5440,7 +5428,7 @@
         <v>46104</v>
       </c>
       <c r="D180" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E180" t="s">
         <v>9</v>
@@ -5463,7 +5451,7 @@
         <v>46104</v>
       </c>
       <c r="D181" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E181" t="s">
         <v>9</v>
@@ -5475,7 +5463,7 @@
         <v>3</v>
       </c>
       <c r="H181" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -5489,7 +5477,7 @@
         <v>46104</v>
       </c>
       <c r="D182" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E182" t="s">
         <v>9</v>
@@ -5512,7 +5500,7 @@
         <v>46118</v>
       </c>
       <c r="D183" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E183" t="s">
         <v>9</v>
@@ -5535,7 +5523,7 @@
         <v>46118</v>
       </c>
       <c r="D184" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E184" t="s">
         <v>9</v>
@@ -5558,7 +5546,7 @@
         <v>46119</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E185" t="s">
         <v>9</v>
@@ -5581,7 +5569,7 @@
         <v>46119</v>
       </c>
       <c r="D186" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E186" t="s">
         <v>9</v>
@@ -5604,7 +5592,7 @@
         <v>46120</v>
       </c>
       <c r="D187" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E187" t="s">
         <v>9</v>
@@ -5627,7 +5615,7 @@
         <v>46126</v>
       </c>
       <c r="D188" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E188" t="s">
         <v>9</v>
@@ -5650,7 +5638,7 @@
         <v>46127</v>
       </c>
       <c r="D189" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E189" t="s">
         <v>9</v>
@@ -5673,7 +5661,7 @@
         <v>46128</v>
       </c>
       <c r="D190" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E190" t="s">
         <v>9</v>
@@ -5696,7 +5684,7 @@
         <v>46128</v>
       </c>
       <c r="D191" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E191" t="s">
         <v>9</v>
@@ -5719,7 +5707,7 @@
         <v>46134</v>
       </c>
       <c r="D192" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E192" t="s">
         <v>9</v>
@@ -5742,7 +5730,7 @@
         <v>46135</v>
       </c>
       <c r="D193" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E193" t="s">
         <v>9</v>
@@ -5754,7 +5742,7 @@
         <v>6</v>
       </c>
       <c r="H193" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -5768,7 +5756,7 @@
         <v>46138</v>
       </c>
       <c r="D194" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E194" t="s">
         <v>12</v>
@@ -5791,7 +5779,7 @@
         <v>46139</v>
       </c>
       <c r="D195" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E195" t="s">
         <v>12</v>
@@ -5814,7 +5802,7 @@
         <v>46145</v>
       </c>
       <c r="D196" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E196" t="s">
         <v>9</v>
@@ -5826,7 +5814,7 @@
         <v>15</v>
       </c>
       <c r="H196" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -5840,7 +5828,7 @@
         <v>46147</v>
       </c>
       <c r="D197" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E197" t="s">
         <v>9</v>
@@ -5852,7 +5840,7 @@
         <v>9</v>
       </c>
       <c r="H197" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -5866,7 +5854,7 @@
         <v>46148</v>
       </c>
       <c r="D198" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E198" t="s">
         <v>9</v>
@@ -5878,7 +5866,7 @@
         <v>5</v>
       </c>
       <c r="H198" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -5892,7 +5880,7 @@
         <v>46153</v>
       </c>
       <c r="D199" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E199" t="s">
         <v>12</v>
@@ -5904,7 +5892,7 @@
         <v>35</v>
       </c>
       <c r="H199" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -5918,7 +5906,7 @@
         <v>46154</v>
       </c>
       <c r="D200" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E200" t="s">
         <v>9</v>
@@ -5930,7 +5918,7 @@
         <v>7</v>
       </c>
       <c r="H200" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -5944,7 +5932,7 @@
         <v>46155</v>
       </c>
       <c r="D201" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
@@ -5967,7 +5955,7 @@
         <v>46160</v>
       </c>
       <c r="D202" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E202" t="s">
         <v>12</v>
@@ -5990,7 +5978,7 @@
         <v>46162</v>
       </c>
       <c r="D203" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E203" t="s">
         <v>9</v>
@@ -6013,7 +6001,7 @@
         <v>46162</v>
       </c>
       <c r="D204" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E204" t="s">
         <v>9</v>
@@ -6036,7 +6024,7 @@
         <v>46162</v>
       </c>
       <c r="D205" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E205" t="s">
         <v>9</v>
@@ -6059,7 +6047,7 @@
         <v>46164</v>
       </c>
       <c r="D206" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E206" t="s">
         <v>9</v>
@@ -6071,7 +6059,7 @@
         <v>18</v>
       </c>
       <c r="H206" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -6085,7 +6073,7 @@
         <v>46165</v>
       </c>
       <c r="D207" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E207" t="s">
         <v>12</v>
@@ -6097,7 +6085,7 @@
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -6111,7 +6099,7 @@
         <v>46168</v>
       </c>
       <c r="D208" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E208" t="s">
         <v>12</v>
@@ -6123,7 +6111,7 @@
         <v>31</v>
       </c>
       <c r="H208" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -6137,7 +6125,7 @@
         <v>46169</v>
       </c>
       <c r="D209" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E209" t="s">
         <v>12</v>
@@ -6160,7 +6148,7 @@
         <v>46167</v>
       </c>
       <c r="D210" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E210" t="s">
         <v>12</v>
@@ -6172,7 +6160,7 @@
         <v>4</v>
       </c>
       <c r="H210" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -6186,7 +6174,7 @@
         <v>46168</v>
       </c>
       <c r="D211" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E211" t="s">
         <v>12</v>
@@ -6198,7 +6186,7 @@
         <v>7</v>
       </c>
       <c r="H211" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -6212,7 +6200,7 @@
         <v>46169</v>
       </c>
       <c r="D212" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E212" t="s">
         <v>9</v>
@@ -6224,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="H212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -6238,7 +6226,7 @@
         <v>46167</v>
       </c>
       <c r="D213" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E213" t="s">
         <v>9</v>
@@ -6261,19 +6249,19 @@
         <v>46174</v>
       </c>
       <c r="D214" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E214" t="s">
         <v>12</v>
       </c>
       <c r="F214" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="G214">
         <v>20</v>
       </c>
       <c r="H214" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -6287,19 +6275,19 @@
         <v>46181</v>
       </c>
       <c r="D215" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E215" t="s">
         <v>9</v>
       </c>
       <c r="F215" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G215">
         <v>25</v>
       </c>
       <c r="H215" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -6313,19 +6301,19 @@
         <v>46189</v>
       </c>
       <c r="D216" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E216" t="s">
         <v>12</v>
       </c>
       <c r="F216" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G216">
         <v>40</v>
       </c>
       <c r="H216" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -6339,19 +6327,19 @@
         <v>46190</v>
       </c>
       <c r="D217" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E217" t="s">
         <v>9</v>
       </c>
       <c r="F217" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G217">
         <v>33</v>
       </c>
       <c r="H217" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -6365,19 +6353,19 @@
         <v>46190</v>
       </c>
       <c r="D218" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E218" t="s">
         <v>9</v>
       </c>
       <c r="F218" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G218">
         <v>3</v>
       </c>
       <c r="H218" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -6391,19 +6379,19 @@
         <v>46190</v>
       </c>
       <c r="D219" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E219" t="s">
         <v>9</v>
       </c>
       <c r="F219" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="G219">
         <v>4</v>
       </c>
       <c r="H219" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -6417,19 +6405,19 @@
         <v>46190</v>
       </c>
       <c r="D220" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E220" t="s">
         <v>9</v>
       </c>
       <c r="F220" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G220">
         <v>14</v>
       </c>
       <c r="H220" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -6443,19 +6431,19 @@
         <v>46190</v>
       </c>
       <c r="D221" t="s">
+        <v>129</v>
+      </c>
+      <c r="E221" t="s">
+        <v>12</v>
+      </c>
+      <c r="F221" t="s">
+        <v>91</v>
+      </c>
+      <c r="G221">
+        <v>9</v>
+      </c>
+      <c r="H221" t="s">
         <v>132</v>
-      </c>
-      <c r="E221" t="s">
-        <v>12</v>
-      </c>
-      <c r="F221" t="s">
-        <v>77</v>
-      </c>
-      <c r="G221">
-        <v>9</v>
-      </c>
-      <c r="H221" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -6469,19 +6457,19 @@
         <v>46190</v>
       </c>
       <c r="D222" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E222" t="s">
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G222">
         <v>30</v>
       </c>
       <c r="H222" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -6495,19 +6483,19 @@
         <v>46190</v>
       </c>
       <c r="D223" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E223" t="s">
         <v>9</v>
       </c>
       <c r="F223" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G223">
         <v>13</v>
       </c>
       <c r="H223" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -6521,19 +6509,19 @@
         <v>46190</v>
       </c>
       <c r="D224" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E224" t="s">
         <v>9</v>
       </c>
       <c r="F224" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G224">
         <v>20</v>
       </c>
       <c r="H224" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
@@ -6547,19 +6535,19 @@
         <v>46190</v>
       </c>
       <c r="D225" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E225" t="s">
         <v>9</v>
       </c>
       <c r="F225" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G225">
         <v>13</v>
       </c>
       <c r="H225" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -6573,19 +6561,19 @@
         <v>46196</v>
       </c>
       <c r="D226" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E226" t="s">
         <v>12</v>
       </c>
       <c r="F226" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G226">
         <v>26</v>
       </c>
       <c r="H226" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -6599,19 +6587,19 @@
         <v>46197</v>
       </c>
       <c r="D227" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E227" t="s">
         <v>12</v>
       </c>
       <c r="F227" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="G227">
         <v>8</v>
       </c>
       <c r="H227" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -6625,19 +6613,19 @@
         <v>46198</v>
       </c>
       <c r="D228" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E228" t="s">
         <v>12</v>
       </c>
       <c r="F228" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="G228">
         <v>5</v>
       </c>
       <c r="H228" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -6651,19 +6639,19 @@
         <v>46203</v>
       </c>
       <c r="D229" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E229" t="s">
         <v>12</v>
       </c>
       <c r="F229" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="G229">
         <v>13</v>
       </c>
       <c r="H229" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
